--- a/data/valuebets_database_2025-07-24.xlsx
+++ b/data/valuebets_database_2025-07-24.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,10 +505,8 @@
           <t>24/07 09:00</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>6.00</t>
-        </is>
+      <c r="F2" t="n">
+        <v>6</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -521,7 +519,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>45862.08158396908</v>
+        <v>45862.08158396991</v>
       </c>
     </row>
     <row r="3">
@@ -550,10 +548,8 @@
           <t>26/07 22:00</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F3" t="n">
+        <v>60</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -566,7 +562,7 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>45862.08158396908</v>
+        <v>45862.08158396991</v>
       </c>
     </row>
     <row r="4">
@@ -595,10 +591,8 @@
           <t>25/07 00:30</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F4" t="n">
+        <v>60</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -611,7 +605,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>45862.08158396908</v>
+        <v>45862.08158396991</v>
       </c>
     </row>
     <row r="5">
@@ -640,10 +634,8 @@
           <t>24/07 10:10</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
+      <c r="F5" t="n">
+        <v>4.5</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -656,7 +648,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>45862.08158396908</v>
+        <v>45862.08158396991</v>
       </c>
     </row>
     <row r="6">
@@ -685,10 +677,8 @@
           <t>25/07 16:45</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F6" t="n">
+        <v>55</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -701,7 +691,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>45862.08158396908</v>
+        <v>45862.08158396991</v>
       </c>
     </row>
     <row r="7">
@@ -730,10 +720,8 @@
           <t>26/07 00:15</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F7" t="n">
+        <v>55</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -746,7 +734,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>45862.08158396908</v>
+        <v>45862.08158396991</v>
       </c>
     </row>
     <row r="8">
@@ -775,10 +763,8 @@
           <t>26/07 18:00</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F8" t="n">
+        <v>55</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -791,7 +777,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>45862.08158396908</v>
+        <v>45862.08158396991</v>
       </c>
     </row>
     <row r="9">
@@ -820,10 +806,8 @@
           <t>26/07 21:30</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F9" t="n">
+        <v>60</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -836,7 +820,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>45862.08158396908</v>
+        <v>45862.08158396991</v>
       </c>
     </row>
     <row r="10">
@@ -865,10 +849,8 @@
           <t>26/07 01:30</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F10" t="n">
+        <v>50</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -881,7 +863,7 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>45862.08158396908</v>
+        <v>45862.08158396991</v>
       </c>
     </row>
     <row r="11">
@@ -910,10 +892,8 @@
           <t>27/07 13:00</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F11" t="n">
+        <v>55</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -926,7 +906,7 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>45862.08158396908</v>
+        <v>45862.08158396991</v>
       </c>
     </row>
     <row r="12">
@@ -955,10 +935,8 @@
           <t>24/07 18:00</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F12" t="n">
+        <v>50</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -971,7 +949,7 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>45862.08158396908</v>
+        <v>45862.08158396991</v>
       </c>
     </row>
     <row r="13">
@@ -1000,10 +978,8 @@
           <t>26/07 15:00</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F13" t="n">
+        <v>55</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1016,7 +992,7 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>45862.08158396908</v>
+        <v>45862.08158396991</v>
       </c>
     </row>
     <row r="14">
@@ -1045,10 +1021,8 @@
           <t>26/07 22:00</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F14" t="n">
+        <v>50</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1061,7 +1035,7 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>45862.08158396908</v>
+        <v>45862.08158396991</v>
       </c>
     </row>
     <row r="15">
@@ -1090,10 +1064,8 @@
           <t>25/07 19:00</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F15" t="n">
+        <v>50</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1106,7 +1078,7 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>45862.08158396908</v>
+        <v>45862.08158396991</v>
       </c>
     </row>
     <row r="16">
@@ -1135,10 +1107,8 @@
           <t>01/08 18:00</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F16" t="n">
+        <v>55</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1151,7 +1121,7 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>45862.08158396908</v>
+        <v>45862.08158396991</v>
       </c>
     </row>
     <row r="17">
@@ -1180,10 +1150,8 @@
           <t>25/07 22:00</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F17" t="n">
+        <v>50</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1196,7 +1164,7 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>45862.08158396908</v>
+        <v>45862.08158396991</v>
       </c>
     </row>
     <row r="18">
@@ -1225,10 +1193,8 @@
           <t>26/07 21:30</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F18" t="n">
+        <v>45</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1241,7 +1207,7 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>45862.08158396908</v>
+        <v>45862.08158396991</v>
       </c>
     </row>
     <row r="19">
@@ -1270,10 +1236,8 @@
           <t>24/07 21:00</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
+      <c r="F19" t="n">
+        <v>2</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1286,7 +1250,7 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>45862.08158396908</v>
+        <v>45862.08158396991</v>
       </c>
     </row>
     <row r="20">
@@ -1315,10 +1279,8 @@
           <t>26/07 23:00</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F20" t="n">
+        <v>50</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1331,7 +1293,7 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>45862.08158396908</v>
+        <v>45862.08158396991</v>
       </c>
     </row>
     <row r="21">
@@ -1360,10 +1322,8 @@
           <t>24/07 10:10</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>10.00</t>
-        </is>
+      <c r="F21" t="n">
+        <v>10</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1376,7 +1336,7 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>45862.08158396908</v>
+        <v>45862.08158396991</v>
       </c>
     </row>
     <row r="22">
@@ -1405,10 +1365,8 @@
           <t>28/07 23:00</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F22" t="n">
+        <v>55</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1421,7 +1379,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>45862.08158396908</v>
+        <v>45862.08158396991</v>
       </c>
     </row>
     <row r="23">
@@ -1450,10 +1408,8 @@
           <t>24/07 17:30</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F23" t="n">
+        <v>45</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1466,7 +1422,7 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>45862.08158396908</v>
+        <v>45862.08158396991</v>
       </c>
     </row>
     <row r="24">
@@ -1495,10 +1451,8 @@
           <t>27/07 11:35</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F24" t="n">
+        <v>50</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1511,7 +1465,7 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>45862.08158396908</v>
+        <v>45862.08158396991</v>
       </c>
     </row>
     <row r="25">
@@ -1540,10 +1494,8 @@
           <t>27/07 18:15</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>35.00</t>
-        </is>
+      <c r="F25" t="n">
+        <v>35</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1556,7 +1508,7 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>45862.08158396908</v>
+        <v>45862.08158396991</v>
       </c>
     </row>
     <row r="26">
@@ -1585,10 +1537,8 @@
           <t>02/08 17:30</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F26" t="n">
+        <v>50</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1601,7 +1551,97 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>45862.08158396908</v>
+        <v>45862.08158396991</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis | X - aces | V.Williams</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>V.Williams – M.FrechWTA - Washington F</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>X - aces</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>24/07 23:30</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>14,9%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>+19,6%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>45862.15374527734</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>PMU(FR)Tennis | Moins que 8.51er set | Shelton, B</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>PMU(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Shelton, Ben – Gabriel DialloEvénements. ATP Washington</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Moins que 8.51er set</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>24/07 19:30</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>7.50</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>14,7%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>+10,2%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>45862.15374527734</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-24.xlsx
+++ b/data/valuebets_database_2025-07-24.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1580,10 +1580,8 @@
           <t>24/07 23:30</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>8.00</t>
-        </is>
+      <c r="F27" t="n">
+        <v>8</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1596,7 +1594,7 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>45862.15374527734</v>
+        <v>45862.15374527778</v>
       </c>
     </row>
     <row r="28">
@@ -1625,10 +1623,8 @@
           <t>24/07 19:30</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>7.50</t>
-        </is>
+      <c r="F28" t="n">
+        <v>7.5</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1641,7 +1637,142 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>45862.15374527734</v>
+        <v>45862.15374527778</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | Gimnasia L</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Gimnasia La Plata – CA IndependienteLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>27/07 19:00</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2,33%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>+4,85%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>45862.19604168533</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | Plus que 4.5 - break | Daniel Eva</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Daniel Evans – Corentin MoutetATP - Washington</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Plus que 4.5 - break</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>24/07 16:10</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>58,2%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>+4,77%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>45862.19604168533</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | CS 2 de Ma</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>CS 2 de Mayo – Club Sportivo LuquenoPrimera Division</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>25/07 21:30</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2,62%</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>+4,74%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>45862.19604168533</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-24.xlsx
+++ b/data/valuebets_database_2025-07-24.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1666,10 +1666,8 @@
           <t>27/07 19:00</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F29" t="n">
+        <v>45</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1682,7 +1680,7 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>45862.19604168533</v>
+        <v>45862.19604168981</v>
       </c>
     </row>
     <row r="30">
@@ -1711,10 +1709,8 @@
           <t>24/07 16:10</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
+      <c r="F30" t="n">
+        <v>1.8</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1727,7 +1723,7 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>45862.19604168533</v>
+        <v>45862.19604168981</v>
       </c>
     </row>
     <row r="31">
@@ -1756,23 +1752,111 @@
           <t>25/07 21:30</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F31" t="n">
+        <v>40</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2,62%</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>+4,74%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>45862.19604168981</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 7.5 - tir cadré | New Englan</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>New England Revolution – CF MontréalÉtats-Unis - États-Unis MLS</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Moins que 7.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>25/07 23:30</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2.95</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>38,0%</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>+12,0%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>45862.22806204839</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Independie</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Independiente Rivadavia – CA BelgranoLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>26/07 00:15</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
         <is>
           <t>40.00</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>2,62%</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>+4,74%</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="n">
-        <v>45862.19604168533</v>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2,66%</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>+6,26%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>45862.22806204839</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-24.xlsx
+++ b/data/valuebets_database_2025-07-24.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1795,10 +1795,8 @@
           <t>25/07 23:30</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2.95</t>
-        </is>
+      <c r="F32" t="n">
+        <v>2.95</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1811,7 +1809,7 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>45862.22806204839</v>
+        <v>45862.22806204861</v>
       </c>
     </row>
     <row r="33">
@@ -1840,10 +1838,8 @@
           <t>26/07 00:15</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F33" t="n">
+        <v>40</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1856,7 +1852,97 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>45862.22806204839</v>
+        <v>45862.22806204861</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | 2 - aces | Arthur Caz</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Arthur Cazaux – Jan-Lennard StruffATP - Kitzbühel</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2 - aces</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>24/07 10:10</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>38,8%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>+26,0%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>45862.27540768738</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football | 21-2- se qualifie | Atletic Es</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Atletic Escaldes – Dinamo TiranaEurope. Europa Conférence (Q)</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>21-2- se qualifie</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>24/07 14:00</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>61,8%</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>+2,65%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>45862.27540768738</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-24.xlsx
+++ b/data/valuebets_database_2025-07-24.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1881,10 +1881,8 @@
           <t>24/07 10:10</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
+      <c r="F34" t="n">
+        <v>3.25</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1897,7 +1895,7 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>45862.27540768738</v>
+        <v>45862.27540768519</v>
       </c>
     </row>
     <row r="35">
@@ -1926,10 +1924,8 @@
           <t>24/07 14:00</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>1.66</t>
-        </is>
+      <c r="F35" t="n">
+        <v>1.66</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1942,7 +1938,277 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>45862.27540768738</v>
+        <v>45862.27540768519</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | Levski Sof</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Levski Sofia – Sporting BragaLigue Europa</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>24/07 17:30</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>65.00</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2,21%</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>+43,4%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>45862.30947310769</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ParionsSport(FR)Tennis | X - aces | D.Evans – </t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>D.Evans – C.MoutetATP - Washington</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>X - aces</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>24/07 16:10</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>12,9%</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>+28,8%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>45862.30947310769</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | 1 - aces | Thiago Sey</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Thiago Seyboth Wild – Botic Van De ZandschulpATP - Kitzbühel</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>24/07 12:30</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>37,1%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>+20,6%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>45862.30947310769</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | EC Juventu</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>EC Juventude – Sao PauloSérie A</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>24/07 22:00</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2,17%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>+19,5%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>45862.30947310769</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis | X - aces | J.Pegula –</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>J.Pegula – L.FernandezWTA - Washington F A9ZJ2X7R 385076e7</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>X - aces</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>24/07 20:10</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>14,8%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>+18,3%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>45862.30947310769</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Deportes T</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Deportes Tolima – Deportivo PereiraPrimera A</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>25/07 23:20</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2,61%</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>+4,43%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>45862.30947310769</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-24.xlsx
+++ b/data/valuebets_database_2025-07-24.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1967,10 +1967,8 @@
           <t>24/07 17:30</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>65.00</t>
-        </is>
+      <c r="F36" t="n">
+        <v>65</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1983,7 +1981,7 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>45862.30947310769</v>
+        <v>45862.30947311343</v>
       </c>
     </row>
     <row r="37">
@@ -2012,10 +2010,8 @@
           <t>24/07 16:10</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>10.00</t>
-        </is>
+      <c r="F37" t="n">
+        <v>10</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2028,7 +2024,7 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>45862.30947310769</v>
+        <v>45862.30947311343</v>
       </c>
     </row>
     <row r="38">
@@ -2057,10 +2053,8 @@
           <t>24/07 12:30</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
+      <c r="F38" t="n">
+        <v>3.25</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2073,7 +2067,7 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>45862.30947310769</v>
+        <v>45862.30947311343</v>
       </c>
     </row>
     <row r="39">
@@ -2102,10 +2096,8 @@
           <t>24/07 22:00</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F39" t="n">
+        <v>55</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2118,7 +2110,7 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>45862.30947310769</v>
+        <v>45862.30947311343</v>
       </c>
     </row>
     <row r="40">
@@ -2147,10 +2139,8 @@
           <t>24/07 20:10</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>8.00</t>
-        </is>
+      <c r="F40" t="n">
+        <v>8</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2163,7 +2153,7 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>45862.30947310769</v>
+        <v>45862.30947311343</v>
       </c>
     </row>
     <row r="41">
@@ -2192,10 +2182,8 @@
           <t>25/07 23:20</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F41" t="n">
+        <v>40</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2208,7 +2196,142 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>45862.30947310769</v>
+        <v>45862.30947311343</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Etoile Rou</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Etoile Rouge Belgrade – OFK BelgradeSuperLiga</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>26/07 18:00</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2,51%</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>+50,5%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>45862.35602057387</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ParionsSport(FR)Tennis | 1 - aces | D.Prizmic </t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>D.Prizmic – L.DarderiATP - Umag</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>24/07 16:00</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>45,7%</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>+14,2%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>45862.35602057387</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | 2 - aces | Pablo Llam</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Pablo Llamas Ruiz – Camilo Ugo CarabelliATP - Umag</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2 - aces</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>24/07 14:30</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>47,5%</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>+4,44%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>45862.35602057387</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-24.xlsx
+++ b/data/valuebets_database_2025-07-24.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I44"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2225,10 +2225,8 @@
           <t>26/07 18:00</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F42" t="n">
+        <v>60</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2241,7 +2239,7 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>45862.35602057387</v>
+        <v>45862.35602057871</v>
       </c>
     </row>
     <row r="43">
@@ -2270,10 +2268,8 @@
           <t>24/07 16:00</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
+      <c r="F43" t="n">
+        <v>2.5</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2286,7 +2282,7 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>45862.35602057387</v>
+        <v>45862.35602057871</v>
       </c>
     </row>
     <row r="44">
@@ -2315,23 +2311,201 @@
           <t>24/07 14:30</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F44" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>47,5%</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>+4,44%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>45862.35602057871</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | FC Sheriff</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>FC Sheriff Tiraspol – UtrechtLigue Europa</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>24/07 17:00</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2,53%</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>+14,1%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>45862.39469813294</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | Plus que 3.5 - break1er participant | Emma Raduc</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Emma Raducanu – Naomi OsakaWTA - Washington</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Plus que 3.5 - break1er participant</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>24/07 17:00</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>59,4%</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>+12,9%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>45862.39469813294</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football | 11-2- se qualifie | Hammarby I</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Hammarby IF – Royal CharleroiEurope. Europa Conférence (Q)</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>11-2- se qualifie</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>24/07 17:00</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
         <is>
           <t>2.20</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>47,5%</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>+4,44%</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="n">
-        <v>45862.35602057387</v>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>48,5%</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>+6,64%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>45862.39469813294</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Football | Plus que 13.5 - tirs2e équipe | Guarani – </t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Guarani – Universidad de ChileInternational - Copa Sudamericana</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Plus que 13.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>24/07 22:00</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>33,0%</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>+5,72%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>45862.39469813294</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-24.xlsx
+++ b/data/valuebets_database_2025-07-24.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:I50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2354,10 +2354,8 @@
           <t>24/07 17:00</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F45" t="n">
+        <v>45</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2370,7 +2368,7 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>45862.39469813294</v>
+        <v>45862.39469813657</v>
       </c>
     </row>
     <row r="46">
@@ -2399,10 +2397,8 @@
           <t>24/07 17:00</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
+      <c r="F46" t="n">
+        <v>1.9</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2415,7 +2411,7 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>45862.39469813294</v>
+        <v>45862.39469813657</v>
       </c>
     </row>
     <row r="47">
@@ -2444,10 +2440,8 @@
           <t>24/07 17:00</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
+      <c r="F47" t="n">
+        <v>2.2</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2460,7 +2454,7 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>45862.39469813294</v>
+        <v>45862.39469813657</v>
       </c>
     </row>
     <row r="48">
@@ -2489,10 +2483,8 @@
           <t>24/07 22:00</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
+      <c r="F48" t="n">
+        <v>3.2</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2505,7 +2497,97 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>45862.39469813294</v>
+        <v>45862.39469813657</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | Plus que 3.5 - break1er participant | Emma Raduc</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Emma Raducanu – Naomi OsakaWTA 500 Washington</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Plus que 3.5 - break1er participant</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>24/07 17:00</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>59,8%</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>+7,54%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>45862.43542568795</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Football | 11-2- se qualifie | Vllaznia S</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Football</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Vllaznia Shkoder – Vikingur ReykjavikLigue Europa Conférence - Éliminatoires A9ZJ2X7R 385076e7</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>11-2- se qualifie</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>24/07 18:30</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>29,2%</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>+5,18%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>45862.43542568795</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-24.xlsx
+++ b/data/valuebets_database_2025-07-24.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:I52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2526,10 +2526,8 @@
           <t>24/07 17:00</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
+      <c r="F49" t="n">
+        <v>1.8</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2542,7 +2540,7 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>45862.43542568795</v>
+        <v>45862.43542568287</v>
       </c>
     </row>
     <row r="50">
@@ -2571,10 +2569,8 @@
           <t>24/07 18:30</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
+      <c r="F50" t="n">
+        <v>3.6</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2587,7 +2583,97 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>45862.43542568795</v>
+        <v>45862.43542568287</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | Sportivo A</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Sportivo Ameliano – Club OlimpiaPrimera Division</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>27/07 18:30</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2,88%</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>+15,4%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>45862.47286354117</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Football | Plus que 12.5 - tirs1re équipe | Juventude </t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Juventude RS – Sao Paulo SPBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Plus que 12.5 - tirs1re équipe</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>24/07 22:00</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>41,4%</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>+13,8%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>45862.47286354117</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-24.xlsx
+++ b/data/valuebets_database_2025-07-24.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I52"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2612,10 +2612,8 @@
           <t>27/07 18:30</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F51" t="n">
+        <v>40</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2628,7 +2626,7 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>45862.47286354117</v>
+        <v>45862.47286354167</v>
       </c>
     </row>
     <row r="52">
@@ -2657,10 +2655,8 @@
           <t>24/07 22:00</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
+      <c r="F52" t="n">
+        <v>2.75</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2673,7 +2669,142 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>45862.47286354117</v>
+        <v>45862.47286354167</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Football | Moins que 9.5 - tirs1re équipe | Juventude </t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Juventude RS – Sao Paulo SPBrésil - Brésil Série A (ADJ98280) 385076e7</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Moins que 9.5 - tirs1re équipe</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>24/07 22:00</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>45,9%</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>+16,9%</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>45862.53506496915</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ParionsSport(FR)Tennis | X - aces | T.Seyboth </t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>T.Seyboth Wild – Van De ZandschATP - Kitzbuhel</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>X - aces</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>24/07 14:10</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>13,5%</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>+7,59%</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>45862.53506496915</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | Tie-break: Oui1er set | Ben Shelto</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ben Shelton – Gabriel DialloATP 500 Washington</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Tie-break: Oui1er set</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>24/07 19:30</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>31,3%</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>+6,38%</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>45862.53506496915</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-24.xlsx
+++ b/data/valuebets_database_2025-07-24.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2698,10 +2698,8 @@
           <t>24/07 22:00</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
+      <c r="F53" t="n">
+        <v>2.55</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2714,7 +2712,7 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>45862.53506496915</v>
+        <v>45862.53506496528</v>
       </c>
     </row>
     <row r="54">
@@ -2743,10 +2741,8 @@
           <t>24/07 14:10</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>8.00</t>
-        </is>
+      <c r="F54" t="n">
+        <v>8</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2759,7 +2755,7 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>45862.53506496915</v>
+        <v>45862.53506496528</v>
       </c>
     </row>
     <row r="55">
@@ -2788,23 +2784,111 @@
           <t>24/07 19:30</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="F55" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>31,3%</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>+6,38%</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>45862.53506496528</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Football | Plus que 5.5 - tir cadré1re équipe | Guarani – </t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Guarani – Universidad de ChileInternational - Copa Sudamericana</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Plus que 5.5 - tir cadré1re équipe</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>24/07 22:00</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
         <is>
           <t>3.40</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>31,3%</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>+6,38%</t>
-        </is>
-      </c>
-      <c r="I55" s="2" t="n">
-        <v>45862.53506496915</v>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>33,3%</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>+13,1%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>45862.56982569927</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | Plus que 6.51er set1er participant | Ben Shelto</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ben Shelton – Gabriel DialloATP 500 Washington</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Plus que 6.51er set1er participant</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>24/07 19:30</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>21,9%</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>+9,32%</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>45862.56982569927</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-24.xlsx
+++ b/data/valuebets_database_2025-07-24.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I57"/>
+  <dimension ref="A1:I60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2827,10 +2827,8 @@
           <t>24/07 22:00</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
+      <c r="F56" t="n">
+        <v>3.4</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2843,7 +2841,7 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>45862.56982569927</v>
+        <v>45862.56982569445</v>
       </c>
     </row>
     <row r="57">
@@ -2872,10 +2870,8 @@
           <t>24/07 19:30</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
+      <c r="F57" t="n">
+        <v>5</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2888,7 +2884,142 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>45862.56982569927</v>
+        <v>45862.56982569445</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Kairat Alm</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Kairat Almaty – KuPS KuopioLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>29/07 15:00</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2,26%</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>+24,1%</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>45862.60093554316</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Football | 1(0:1)1re période | Midtjyllan</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Football</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Midtjylland – HibernianLigue Europa UEFA - Éliminatoires</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>1(0:1)1re période</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>24/07 17:30</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>27,7%</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>+10,9%</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>45862.60093554316</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | Tatran Pre</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Tatran Presov – Slovan BratislavaFortuna Liga</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>26/07 18:30</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2,64%</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>+5,47%</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>45862.60093554316</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-24.xlsx
+++ b/data/valuebets_database_2025-07-24.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I60"/>
+  <dimension ref="A1:I64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2913,10 +2913,8 @@
           <t>29/07 15:00</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F58" t="n">
+        <v>55</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2929,7 +2927,7 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>45862.60093554316</v>
+        <v>45862.60093554398</v>
       </c>
     </row>
     <row r="59">
@@ -2958,10 +2956,8 @@
           <t>24/07 17:30</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
+      <c r="F59" t="n">
+        <v>4</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2974,7 +2970,7 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>45862.60093554316</v>
+        <v>45862.60093554398</v>
       </c>
     </row>
     <row r="60">
@@ -3003,10 +2999,8 @@
           <t>26/07 18:30</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F60" t="n">
+        <v>40</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -3019,7 +3013,187 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>45862.60093554316</v>
+        <v>45862.60093554398</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.52e équipe | Fortaleza </t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Fortaleza FC – Alianza FC ValleduparPrimera A</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>28/07 01:20</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>2,71%</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>+62,9%</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>45862.64115693792</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.52e équipe | Deportivo </t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Deportivo Cali – Fortaleza FCPrimera A</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>25/07 01:10</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>2,43%</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>+46,0%</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>45862.64115693792</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Envigado F</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Envigado FC – La EquidadPrimera A</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>27/07 21:00</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>2,74%</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>+23,4%</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>45862.64115693792</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PMU(FR)Football | 21-2- se qualifie | FC Pyunik </t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>FC Pyunik – Gyori EtoEurope. Europa Conférence (Q)</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>21-2- se qualifie</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>24/07 16:00</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>54,8%</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>+9,64%</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>45862.64115693792</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-24.xlsx
+++ b/data/valuebets_database_2025-07-24.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I64"/>
+  <dimension ref="A1:I66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3042,10 +3042,8 @@
           <t>28/07 01:20</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F61" t="n">
+        <v>60</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -3058,7 +3056,7 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>45862.64115693792</v>
+        <v>45862.64115693287</v>
       </c>
     </row>
     <row r="62">
@@ -3087,10 +3085,8 @@
           <t>25/07 01:10</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F62" t="n">
+        <v>60</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -3103,7 +3099,7 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>45862.64115693792</v>
+        <v>45862.64115693287</v>
       </c>
     </row>
     <row r="63">
@@ -3132,10 +3128,8 @@
           <t>27/07 21:00</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F63" t="n">
+        <v>45</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -3148,7 +3142,7 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>45862.64115693792</v>
+        <v>45862.64115693287</v>
       </c>
     </row>
     <row r="64">
@@ -3177,10 +3171,8 @@
           <t>24/07 16:00</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
+      <c r="F64" t="n">
+        <v>2</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -3193,7 +3185,97 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>45862.64115693792</v>
+        <v>45862.64115693287</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 23.5 - tirs | Besiktas –</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Besiktas – Shakhtar DonetskEurope - Ligue Europa</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Plus que 23.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>24/07 18:00</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>55,2%</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>+11,5%</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>45862.6864324499</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football | 21-2- se qualifie | Hammarby I</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Hammarby IF – Royal CharleroiEurope. Europa Conférence (Q)</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>21-2- se qualifie</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>24/07 17:00</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>52,5%</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>+10,2%</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>45862.6864324499</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-24.xlsx
+++ b/data/valuebets_database_2025-07-24.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I66"/>
+  <dimension ref="A1:I68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3214,10 +3214,8 @@
           <t>24/07 18:00</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>2.02</t>
-        </is>
+      <c r="F65" t="n">
+        <v>2.02</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -3230,7 +3228,7 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>45862.6864324499</v>
+        <v>45862.6864324537</v>
       </c>
     </row>
     <row r="66">
@@ -3259,10 +3257,8 @@
           <t>24/07 17:00</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
+      <c r="F66" t="n">
+        <v>2.1</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -3275,7 +3271,97 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>45862.6864324499</v>
+        <v>45862.6864324537</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | 1 - aces | Taylor Fri</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Taylor Fritz – Matteo Arnaldi385076e7 ATP - Washington</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>24/07 22:00</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>84,0%</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>+5,05%</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="n">
+        <v>45862.72337711711</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.52e équipe | FC Bâle – </t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>FC Bâle – Grasshopper ZurichSuper League</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>02/08 18:30</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>2,06%</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>+3,07%</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>45862.72337711711</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-24.xlsx
+++ b/data/valuebets_database_2025-07-24.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I68"/>
+  <dimension ref="A1:I71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3300,10 +3300,8 @@
           <t>24/07 22:00</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
+      <c r="F67" t="n">
+        <v>1.25</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -3316,7 +3314,7 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>45862.72337711711</v>
+        <v>45862.72337711805</v>
       </c>
     </row>
     <row r="68">
@@ -3345,10 +3343,8 @@
           <t>02/08 18:30</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F68" t="n">
+        <v>50</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -3361,7 +3357,142 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>45862.72337711711</v>
+        <v>45862.72337711805</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Football | 21-2- se qualifie | Dinamo Min</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Football</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Dinamo Minsk – Egnatia RrogozhineLigue Europa Conférence - Éliminatoires</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>21-2- se qualifie</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>24/07 18:45</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>30,3%</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>+9,09%</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="n">
+        <v>45862.77464542651</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Basketball | X1re période[race to 15 regular time] | Los Angele</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Basketball</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Los Angeles Sparks – Connecticut SunUSA - WNBA</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>X1re période[race to 15 regular time]</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>24/07 23:00</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>46.00</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>2,35%</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>+8,31%</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>45862.77464542651</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Pas de buts | KR Reykjav</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>KR Reykjavik – Breidablik KopavogurIslande - Islande Úrvalsdeild</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>26/07 17:00</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>35.00</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>2,97%</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>+3,93%</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="n">
+        <v>45862.77464542651</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-24.xlsx
+++ b/data/valuebets_database_2025-07-24.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I71"/>
+  <dimension ref="A1:I72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3386,10 +3386,8 @@
           <t>24/07 18:45</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
+      <c r="F69" t="n">
+        <v>3.6</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -3402,7 +3400,7 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>45862.77464542651</v>
+        <v>45862.77464542824</v>
       </c>
     </row>
     <row r="70">
@@ -3431,10 +3429,8 @@
           <t>24/07 23:00</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>46.00</t>
-        </is>
+      <c r="F70" t="n">
+        <v>46</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -3447,7 +3443,7 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>45862.77464542651</v>
+        <v>45862.77464542824</v>
       </c>
     </row>
     <row r="71">
@@ -3476,10 +3472,8 @@
           <t>26/07 17:00</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>35.00</t>
-        </is>
+      <c r="F71" t="n">
+        <v>35</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -3492,7 +3486,52 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>45862.77464542651</v>
+        <v>45862.77464542824</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Pas de buts | Bodø/Glimt</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Bodø/Glimt – Strømsgodset IFNorvège - Norvège Eliteserien</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>30/07 17:00</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>1,71%</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>+2,72%</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="n">
+        <v>45862.80575344243</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-24.xlsx
+++ b/data/valuebets_database_2025-07-24.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I72"/>
+  <dimension ref="A1:I75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3515,10 +3515,8 @@
           <t>30/07 17:00</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F72" t="n">
+        <v>60</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -3531,7 +3529,142 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>45862.80575344243</v>
+        <v>45862.8057534375</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Football | Moins que 12.5 - tirs2e équipe | Juventude </t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Juventude RS – Sao Paulo SPBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Moins que 12.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>24/07 22:00</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>33,1%</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>+5,93%</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="n">
+        <v>45862.85056637813</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | Dinamo Buc</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Dinamo Bucarest – FCSBLiga 1</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>02/08 18:30</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>35.00</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>2,92%</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>+2,17%</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="n">
+        <v>45862.85056637813</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | SK Sigma O</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>SK Sigma Olomouc – FK Dukla PragueSynot League</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>26/07 15:00</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>2,55%</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>+1,93%</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="n">
+        <v>45862.85056637813</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-24.xlsx
+++ b/data/valuebets_database_2025-07-24.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I75"/>
+  <dimension ref="A1:I76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3558,10 +3558,8 @@
           <t>24/07 22:00</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
+      <c r="F73" t="n">
+        <v>3.2</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -3574,7 +3572,7 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>45862.85056637813</v>
+        <v>45862.85056637732</v>
       </c>
     </row>
     <row r="74">
@@ -3603,10 +3601,8 @@
           <t>02/08 18:30</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>35.00</t>
-        </is>
+      <c r="F74" t="n">
+        <v>35</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -3619,7 +3615,7 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>45862.85056637813</v>
+        <v>45862.85056637732</v>
       </c>
     </row>
     <row r="75">
@@ -3648,10 +3644,8 @@
           <t>26/07 15:00</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F75" t="n">
+        <v>40</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -3664,7 +3658,52 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>45862.85056637813</v>
+        <v>45862.85056637732</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis | X - aces | E.Raducanu</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>E.Raducanu – M.SakkariWTA - Washington F</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>X - aces</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>25/07 16:00</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>14,6%</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>+16,7%</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="n">
+        <v>45862.89101898074</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-24.xlsx
+++ b/data/valuebets_database_2025-07-24.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I76"/>
+  <dimension ref="A1:I77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3687,10 +3687,8 @@
           <t>25/07 16:00</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>8.00</t>
-        </is>
+      <c r="F76" t="n">
+        <v>8</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -3703,7 +3701,52 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>45862.89101898074</v>
+        <v>45862.89101898149</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Hajduk Spl</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Hajduk Split – Istra 1961HNL</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>03/08 19:00</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>2,14%</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>+7,04%</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="n">
+        <v>45862.93274459441</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-24.xlsx
+++ b/data/valuebets_database_2025-07-24.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I77"/>
+  <dimension ref="A1:I80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3730,23 +3730,156 @@
           <t>03/08 19:00</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
+      <c r="F77" t="n">
+        <v>50</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>2,14%</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>+7,04%</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="n">
+        <v>45862.93274459491</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 2.52e équipe | Etoile Rou</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Etoile Rouge Belgrade – Lincoln Red Imps FCLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Plus que 2.52e équipe</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>29/07 19:00</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>2,01%</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>+10,4%</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>45862.97468175176</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Fluminense</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Fluminense – GremioSérie A</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>03/08 00:00</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
         <is>
           <t>50.00</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>2,14%</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>+7,04%</t>
-        </is>
-      </c>
-      <c r="I77" s="2" t="n">
-        <v>45862.93274459441</v>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>2,12%</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>+5,82%</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="n">
+        <v>45862.97468175176</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Tennis | H 2 (+1.5)1er set | Bublik – B</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Bublik – Bot Van de ZandschulpATP Kitzbuhel 2025</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>H 2 (+1.5)1er set</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>25/07 12:30</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>45,5%</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>+2,41%</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>45862.97468175176</v>
       </c>
     </row>
   </sheetData>
